--- a/src/utils/sxsyzlzq/wuqi/zz_shenqi_shengji.xlsx
+++ b/src/utils/sxsyzlzq/wuqi/zz_shenqi_shengji.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\keyuanWeb\src\utils\sxsyzlzq\wuqi\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13395"/>
+    <workbookView windowWidth="11985" windowHeight="9795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
   <si>
     <t>蓝色</t>
   </si>
@@ -89,6 +94,12 @@
   </si>
   <si>
     <t>12-13星</t>
+  </si>
+  <si>
+    <t>13-14星</t>
+  </si>
+  <si>
+    <t>14-15星</t>
   </si>
   <si>
     <t>紫色</t>
@@ -1025,7 +1036,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1051,7 +1062,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:2">
+    <row r="2" hidden="1" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1059,7 +1070,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1067,7 +1078,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1078,7 +1089,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1089,7 +1100,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1100,7 +1111,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1257,69 +1268,90 @@
         <v>2795</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" hidden="1" spans="1:2">
+      <c r="B15">
+        <v>14000</v>
+      </c>
+      <c r="C15">
+        <v>1500</v>
+      </c>
+      <c r="D15">
+        <v>2400</v>
+      </c>
+      <c r="E15">
+        <v>1450</v>
+      </c>
+      <c r="F15">
+        <v>960</v>
+      </c>
+      <c r="G15">
+        <v>3755</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16">
+        <v>18000</v>
+      </c>
+      <c r="C16">
+        <v>2000</v>
+      </c>
+      <c r="D16">
+        <v>3100</v>
+      </c>
+      <c r="E16">
+        <v>1900</v>
+      </c>
+      <c r="F16">
+        <v>1250</v>
+      </c>
+      <c r="G16">
+        <v>5005</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" hidden="1" spans="1:7">
+      <c r="A18" t="s">
         <v>7</v>
       </c>
-      <c r="B16">
+      <c r="B18">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
         <v>8</v>
       </c>
-      <c r="B17">
+      <c r="B19">
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
         <v>9</v>
       </c>
-      <c r="B18">
+      <c r="B20">
         <v>120</v>
       </c>
-      <c r="E18">
+      <c r="E20">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
         <v>10</v>
       </c>
-      <c r="B19">
+      <c r="B21">
         <v>300</v>
-      </c>
-      <c r="E19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20">
-        <v>600</v>
-      </c>
-      <c r="E20">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21">
-        <v>150</v>
-      </c>
-      <c r="D21">
-        <v>500</v>
       </c>
       <c r="E21">
         <v>90</v>
@@ -1327,356 +1359,473 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22">
-        <v>260</v>
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>600</v>
       </c>
       <c r="E22">
-        <v>480</v>
-      </c>
-      <c r="F22">
-        <v>80</v>
-      </c>
-      <c r="G22">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C23">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="D23">
-        <v>480</v>
-      </c>
-      <c r="F23">
-        <v>480</v>
-      </c>
-      <c r="G23">
-        <v>560</v>
+        <v>500</v>
+      </c>
+      <c r="E23">
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24">
-        <v>750</v>
-      </c>
-      <c r="D24">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="E24">
-        <v>800</v>
+        <v>480</v>
       </c>
       <c r="F24">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="G24">
-        <v>1160</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C25">
-        <v>1200</v>
+        <v>450</v>
       </c>
       <c r="D25">
-        <v>1500</v>
-      </c>
-      <c r="E25">
-        <v>1500</v>
+        <v>480</v>
       </c>
       <c r="F25">
-        <v>900</v>
+        <v>480</v>
       </c>
       <c r="G25">
-        <v>2060</v>
+        <v>560</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26">
-        <v>7500</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>1200</v>
+        <v>750</v>
       </c>
       <c r="D26">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E26">
-        <v>1800</v>
+        <v>800</v>
       </c>
       <c r="F26">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="G26">
-        <v>3060</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27">
-        <v>12000</v>
+        <v>16</v>
       </c>
       <c r="C27">
+        <v>1200</v>
+      </c>
+      <c r="D27">
         <v>1500</v>
       </c>
-      <c r="D27">
-        <v>3000</v>
-      </c>
       <c r="E27">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="F27">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="G27">
-        <v>4260</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28">
+        <v>7500</v>
+      </c>
+      <c r="C28">
+        <v>1200</v>
+      </c>
+      <c r="D28">
+        <v>2000</v>
+      </c>
+      <c r="E28">
+        <v>1800</v>
+      </c>
+      <c r="F28">
+        <v>1000</v>
+      </c>
+      <c r="G28">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29">
+        <v>12000</v>
+      </c>
+      <c r="C29">
+        <v>1500</v>
+      </c>
+      <c r="D29">
+        <v>3000</v>
+      </c>
+      <c r="E29">
+        <v>2200</v>
+      </c>
+      <c r="F29">
+        <v>1200</v>
+      </c>
+      <c r="G29">
+        <v>4260</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
         <v>19</v>
       </c>
-      <c r="B28">
+      <c r="B30">
         <v>15000</v>
       </c>
-      <c r="C28">
+      <c r="C30">
         <v>1800</v>
       </c>
-      <c r="D28">
+      <c r="D30">
         <v>3500</v>
       </c>
-      <c r="E28">
+      <c r="E30">
         <v>2500</v>
       </c>
-      <c r="F28">
+      <c r="F30">
         <v>1500</v>
       </c>
-      <c r="G28">
+      <c r="G30">
         <v>5760</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31">
+        <v>19000</v>
+      </c>
+      <c r="C31">
+        <v>2160</v>
+      </c>
+      <c r="D31">
+        <v>4200</v>
+      </c>
+      <c r="E31">
+        <v>3000</v>
+      </c>
+      <c r="F31">
+        <v>1800</v>
+      </c>
+      <c r="G31">
+        <v>7560</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="30" hidden="1" spans="1:2">
-      <c r="A30" t="s">
+      <c r="B32">
+        <v>25000</v>
+      </c>
+      <c r="C32">
+        <v>2800</v>
+      </c>
+      <c r="D32">
+        <v>5500</v>
+      </c>
+      <c r="E32">
+        <v>3900</v>
+      </c>
+      <c r="F32">
+        <v>2150</v>
+      </c>
+      <c r="G32">
+        <v>9710</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" hidden="1" spans="1:7">
+      <c r="A34" t="s">
         <v>7</v>
       </c>
-      <c r="B30">
+      <c r="B34">
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
         <v>8</v>
       </c>
-      <c r="B31">
+      <c r="B35">
         <v>90</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32">
-        <v>200</v>
-      </c>
-      <c r="F32">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33">
-        <v>500</v>
-      </c>
-      <c r="F33">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34">
-        <v>900</v>
-      </c>
-      <c r="F34">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35">
-        <v>240</v>
-      </c>
-      <c r="D35">
-        <v>1000</v>
-      </c>
-      <c r="E35">
-        <v>160</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36">
-        <v>400</v>
-      </c>
-      <c r="E36">
-        <v>900</v>
+        <v>9</v>
+      </c>
+      <c r="B36">
+        <v>200</v>
       </c>
       <c r="F36">
-        <v>125</v>
-      </c>
-      <c r="G36">
-        <v>125</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37">
-        <v>680</v>
-      </c>
-      <c r="D37">
-        <v>900</v>
+        <v>10</v>
+      </c>
+      <c r="B37">
+        <v>500</v>
       </c>
       <c r="F37">
-        <v>900</v>
-      </c>
-      <c r="G37">
-        <v>1025</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38">
-        <v>1000</v>
-      </c>
-      <c r="D38">
-        <v>1500</v>
-      </c>
-      <c r="E38">
-        <v>1200</v>
+        <v>11</v>
+      </c>
+      <c r="B38">
+        <v>900</v>
       </c>
       <c r="F38">
-        <v>1000</v>
-      </c>
-      <c r="G38">
-        <v>2025</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C39">
-        <v>1600</v>
+        <v>240</v>
       </c>
       <c r="D39">
-        <v>2400</v>
+        <v>1000</v>
       </c>
       <c r="E39">
-        <v>2000</v>
-      </c>
-      <c r="F39">
-        <v>1800</v>
-      </c>
-      <c r="G39">
-        <v>3825</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40">
-        <v>10000</v>
+        <v>13</v>
       </c>
       <c r="C40">
-        <v>1600</v>
-      </c>
-      <c r="D40">
-        <v>3200</v>
+        <v>400</v>
       </c>
       <c r="E40">
-        <v>2400</v>
+        <v>900</v>
       </c>
       <c r="F40">
-        <v>2000</v>
+        <v>125</v>
       </c>
       <c r="G40">
-        <v>5825</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>18</v>
-      </c>
-      <c r="B41">
-        <v>16000</v>
+        <v>14</v>
       </c>
       <c r="C41">
-        <v>2000</v>
+        <v>680</v>
       </c>
       <c r="D41">
-        <v>4000</v>
-      </c>
-      <c r="E41">
-        <v>3000</v>
+        <v>900</v>
       </c>
       <c r="F41">
-        <v>2400</v>
+        <v>900</v>
       </c>
       <c r="G41">
-        <v>8225</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42">
+        <v>1000</v>
+      </c>
+      <c r="D42">
+        <v>1500</v>
+      </c>
+      <c r="E42">
+        <v>1200</v>
+      </c>
+      <c r="F42">
+        <v>1000</v>
+      </c>
+      <c r="G42">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43">
+        <v>1600</v>
+      </c>
+      <c r="D43">
+        <v>2400</v>
+      </c>
+      <c r="E43">
+        <v>2000</v>
+      </c>
+      <c r="F43">
+        <v>1800</v>
+      </c>
+      <c r="G43">
+        <v>3825</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44">
+        <v>10000</v>
+      </c>
+      <c r="C44">
+        <v>1600</v>
+      </c>
+      <c r="D44">
+        <v>3200</v>
+      </c>
+      <c r="E44">
+        <v>2400</v>
+      </c>
+      <c r="F44">
+        <v>2000</v>
+      </c>
+      <c r="G44">
+        <v>5825</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45">
+        <v>16000</v>
+      </c>
+      <c r="C45">
+        <v>2000</v>
+      </c>
+      <c r="D45">
+        <v>4000</v>
+      </c>
+      <c r="E45">
+        <v>3000</v>
+      </c>
+      <c r="F45">
+        <v>2400</v>
+      </c>
+      <c r="G45">
+        <v>8225</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
         <v>19</v>
       </c>
-      <c r="B42">
+      <c r="B46">
         <v>20000</v>
       </c>
-      <c r="C42">
+      <c r="C46">
         <v>2400</v>
       </c>
-      <c r="D42">
+      <c r="D46">
         <v>4500</v>
       </c>
-      <c r="E42">
+      <c r="E46">
         <v>3500</v>
       </c>
-      <c r="F42">
+      <c r="F46">
         <v>2800</v>
       </c>
-      <c r="G42">
+      <c r="G46">
         <v>11025</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B47">
+        <v>26000</v>
+      </c>
+      <c r="C47">
+        <v>2880</v>
+      </c>
+      <c r="D47">
+        <v>5400</v>
+      </c>
+      <c r="E47">
+        <v>4200</v>
+      </c>
+      <c r="F47">
+        <v>3360</v>
+      </c>
+      <c r="G47">
+        <v>14385</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48">
+        <v>33800</v>
+      </c>
+      <c r="C48">
+        <v>3744</v>
+      </c>
+      <c r="D48">
+        <v>7000</v>
+      </c>
+      <c r="E48">
+        <v>5460</v>
+      </c>
+      <c r="F48">
+        <v>4368</v>
+      </c>
+      <c r="G48">
+        <v>18753</v>
       </c>
     </row>
   </sheetData>
